--- a/rules/CORE-000355/negative/01/data/unit-test-coreid-CG0014-negative.xlsx
+++ b/rules/CORE-000355/negative/01/data/unit-test-coreid-CG0014-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\els_janssens\CORE\Rule_Authoring\core-contributor\rules\CORE-000355\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9EF0071-63A8-43BF-B821-70C7989EE797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE904C0F-D7D6-417D-BB92-6F3573E9524B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="218">
   <si>
     <t>Product</t>
   </si>
@@ -61,9 +61,6 @@
     <t>lb.xpt</t>
   </si>
   <si>
-    <t>Labotory Results</t>
-  </si>
-  <si>
     <t>ex.xpt</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
     <t>USUBJID</t>
   </si>
   <si>
-    <t>AESEQ</t>
-  </si>
-  <si>
     <t>AETERM</t>
   </si>
   <si>
@@ -665,6 +659,27 @@
   </si>
   <si>
     <t>2005-10-16T00:00:00.000Z</t>
+  </si>
+  <si>
+    <t>Laboratory Results</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>$missing_required_variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AESEQ; AEDECOD </t>
+  </si>
+  <si>
+    <t>LBTEST</t>
+  </si>
+  <si>
+    <t>EXTRT</t>
   </si>
 </sst>
 </file>
@@ -710,7 +725,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -725,12 +740,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -768,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -777,14 +786,12 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1155,6 +1162,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1185,1512 +1195,134 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B3 A5:B5 A4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>212</v>
+      </c>
+      <c r="D2" t="s">
+        <v>213</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>212</v>
+      </c>
+      <c r="D3" t="s">
+        <v>213</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>214</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
+        <v>214</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>213</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
-        <v>2</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
-        <v>2</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
-        <v>2</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="15">
-        <v>2</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
-        <v>2</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="15">
-        <v>2</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
-        <v>2</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
-        <v>2</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="15">
-        <v>2</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
-        <v>2</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
-        <v>2</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
-        <v>2</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="15">
-        <v>2</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
-        <v>2</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
-        <v>2</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
-        <v>2</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15">
-        <v>2</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="15">
-        <v>2</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="15">
-        <v>2</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="15">
-        <v>2</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="15">
-        <v>2</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="15">
-        <v>2</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="15">
-        <v>2</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
-        <v>3</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15">
-        <v>3</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
-        <v>3</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>18</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="15">
-        <v>3</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
-        <v>3</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15">
-        <v>3</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
-        <v>3</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s">
-        <v>18</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
-        <v>3</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
-        <v>3</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
-        <v>3</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
-        <v>3</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="15">
-        <v>3</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="15">
-        <v>3</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="15">
-        <v>3</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="15">
-        <v>3</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="15">
-        <v>3</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
-        <v>3</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="15">
-        <v>3</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="15">
-        <v>3</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" t="s">
-        <v>18</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>3</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="15">
-        <v>3</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="15">
-        <v>3</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="15">
-        <v>3</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="15">
-        <v>3</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="15">
-        <v>3</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="15">
-        <v>4</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" t="s">
-        <v>18</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="15">
-        <v>4</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" t="s">
-        <v>18</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="15">
-        <v>4</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" t="s">
-        <v>18</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="15">
-        <v>4</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" t="s">
-        <v>18</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="15">
-        <v>4</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="15">
-        <v>4</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" t="s">
-        <v>18</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="15">
-        <v>4</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" t="s">
-        <v>18</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="15">
-        <v>4</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C66" t="s">
-        <v>18</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="15">
-        <v>4</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="15">
-        <v>4</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="15">
-        <v>4</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" t="s">
-        <v>18</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="15">
-        <v>4</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="15">
-        <v>4</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" t="s">
-        <v>18</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="15">
-        <v>4</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" t="s">
-        <v>18</v>
-      </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="15">
-        <v>4</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C73" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="15">
-        <v>4</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C74" t="s">
-        <v>18</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>191</v>
+        <v>214</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2706,97 +1338,101 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="17.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2830,176 +1466,176 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="E7" s="6">
         <v>2</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="H8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" s="6">
         <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="6">
         <v>2</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="H10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3012,233 +1648,224 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="V1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="W1" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="V2" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>41</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>50</v>
       </c>
@@ -3249,7 +1876,7 @@
         <v>50</v>
       </c>
       <c r="D4" s="3">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3">
         <v>50</v>
@@ -3297,229 +1924,217 @@
         <v>50</v>
       </c>
       <c r="T4" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="U4" s="3">
         <v>8</v>
       </c>
       <c r="V4" s="3">
-        <v>8</v>
-      </c>
-      <c r="W4" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="13" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="2">
+        <v>123101</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="13">
-        <v>123101</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="S5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
+      </c>
+      <c r="T5" s="2">
+        <v>-1</v>
       </c>
       <c r="U5" s="2">
         <v>-1</v>
       </c>
-      <c r="V5" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="13">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2">
         <v>123101</v>
       </c>
-      <c r="D6" s="2">
-        <v>2</v>
+      <c r="D6" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" t="s">
-        <v>20</v>
-      </c>
-      <c r="P6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>109</v>
+      <c r="T6" s="2">
+        <v>1</v>
       </c>
       <c r="U6" s="2">
         <v>1</v>
       </c>
-      <c r="V6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="13">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="2">
         <v>123101</v>
       </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T7" s="2">
+        <v>9</v>
+      </c>
+      <c r="U7" t="s">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" t="s">
-        <v>20</v>
-      </c>
-      <c r="O7" t="s">
-        <v>20</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="R7" t="s">
-        <v>20</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T7" t="s">
-        <v>20</v>
-      </c>
-      <c r="U7" s="2">
-        <v>9</v>
-      </c>
-      <c r="V7" t="s">
-        <v>20</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W4 A7:W7 B5:W5 A6:B6 D6:W6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C4 A7:C7 B5:C5 A6:B6 D6:V6 D1:V4 D7:V7 D5:V5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3528,254 +2143,258 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AA369"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="T1" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="W1" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="U1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="8" t="s">
+      <c r="X1" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="Y1" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="X1" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>137</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="U2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>20</v>
+      <c r="Z2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="N3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="W3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>20</v>
+      <c r="Z3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -3854,2148 +2473,2148 @@
       <c r="Y4" s="3">
         <v>8</v>
       </c>
-      <c r="Z4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>20</v>
+      <c r="Z4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5" s="2">
         <v>123101</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M5" s="2">
         <v>4.46</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>19</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="O5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="T5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V5" s="2">
         <v>100</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Y5" s="2">
         <v>-15</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>20</v>
+      <c r="Z5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6" s="2">
         <v>123101</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="10">
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M6" s="2">
         <v>4.3099999999999996</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="O6" t="s">
-        <v>20</v>
-      </c>
-      <c r="P6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>20</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="T6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V6" s="2">
         <v>200</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Y6" s="2">
         <v>1</v>
       </c>
       <c r="Z6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7" s="2">
         <v>123101</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="10">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M7" s="2">
         <v>3.62</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>19</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="O7" t="s">
-        <v>20</v>
-      </c>
-      <c r="P7" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>20</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="T7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V7" s="2">
         <v>2200</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="Y7" s="2">
         <v>141</v>
       </c>
       <c r="Z7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C8" s="2">
         <v>123101</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="10">
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M8" s="2">
         <v>4.17</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O8" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="O8" t="s">
-        <v>20</v>
-      </c>
-      <c r="P8" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>20</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="T8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V8" s="2">
         <v>2900</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Y8" s="2">
         <v>213</v>
       </c>
       <c r="Z8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -6010,182 +4629,185 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="N1" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="O1" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>191</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="Q2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="Q3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -6238,27 +4860,27 @@
         <v>8</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C5" s="2">
         <v>123101</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -6267,28 +4889,28 @@
         <v>54</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="O5" s="2">
         <v>1</v>
@@ -6297,21 +4919,21 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C6" s="2">
         <v>123101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
@@ -6320,28 +4942,28 @@
         <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="O6" s="2">
         <v>2</v>
@@ -6350,27 +4972,27 @@
         <v>2</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2">
         <v>123101</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E7" s="2">
         <v>3</v>
@@ -6379,28 +5001,28 @@
         <v>54</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="N7" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="O7" s="2">
         <v>3</v>
@@ -6409,27 +5031,27 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2">
         <v>123101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E8" s="2">
         <v>4</v>
@@ -6438,28 +5060,28 @@
         <v>54</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="O8" s="2">
         <v>4</v>
@@ -6468,13 +5090,13 @@
         <v>4</v>
       </c>
       <c r="Q8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
